--- a/data/trans_orig/P63-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P63-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si la persona entrevistada ha trabajado anteriormente en 2007</t>
+          <t>Población según si la persona entrevistada ha trabajado anteriormente en 2007 (tasa de respuesta: 99,97%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>598759</t>
+          <t>598212</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>622686</t>
+          <t>621599</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>91,9%</t>
+          <t>91,82%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>95,57%</t>
+          <t>95,41%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>436681</t>
+          <t>435543</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>502700</t>
+          <t>502909</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>37,59%</t>
+          <t>37,5%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>43,28%</t>
+          <t>43,3%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1039115</t>
+          <t>1039430</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1121072</t>
+          <t>1122738</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>57,31%</t>
+          <t>57,33%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>61,83%</t>
+          <t>61,92%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>28832</t>
+          <t>29919</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>52759</t>
+          <t>53306</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>658870</t>
+          <t>658661</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>724889</t>
+          <t>726027</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>56,72%</t>
+          <t>56,7%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>62,41%</t>
+          <t>62,5%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>692016</t>
+          <t>690350</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>773973</t>
+          <t>773658</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>38,17%</t>
+          <t>38,08%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>42,69%</t>
+          <t>42,67%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>318131</t>
+          <t>318391</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>363985</t>
+          <t>364139</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>56,23%</t>
+          <t>56,27%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>64,33%</t>
+          <t>64,36%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>477119</t>
+          <t>476117</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>538850</t>
+          <t>541473</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>47,6%</t>
+          <t>47,5%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>53,76%</t>
+          <t>54,02%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>809840</t>
+          <t>812634</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>886264</t>
+          <t>887938</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>51,64%</t>
+          <t>51,82%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>56,52%</t>
+          <t>56,62%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>201814</t>
+          <t>201660</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>247668</t>
+          <t>247408</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>35,67%</t>
+          <t>35,64%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>43,77%</t>
+          <t>43,73%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>463460</t>
+          <t>460837</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>525191</t>
+          <t>526193</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>46,24%</t>
+          <t>45,98%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>52,4%</t>
+          <t>52,5%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>681845</t>
+          <t>680171</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>758269</t>
+          <t>755475</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>43,48%</t>
+          <t>43,38%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>48,36%</t>
+          <t>48,18%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>101224</t>
+          <t>102126</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>121988</t>
+          <t>122997</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>69,29%</t>
+          <t>69,9%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>83,5%</t>
+          <t>84,19%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>109097</t>
+          <t>110955</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>136070</t>
+          <t>136328</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>58,95%</t>
+          <t>59,96%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>73,53%</t>
+          <t>73,67%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>218092</t>
+          <t>222265</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>252651</t>
+          <t>253720</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>65,86%</t>
+          <t>67,12%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>76,29%</t>
+          <t>76,62%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>24110</t>
+          <t>23101</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>44874</t>
+          <t>43972</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>15,81%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>30,71%</t>
+          <t>30,1%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>48984</t>
+          <t>48726</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>75957</t>
+          <t>74099</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>26,47%</t>
+          <t>26,33%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>41,05%</t>
+          <t>40,04%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>78501</t>
+          <t>77432</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>113060</t>
+          <t>108887</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>23,38%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>34,14%</t>
+          <t>32,88%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1032624</t>
+          <t>1034857</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1092730</t>
+          <t>1096006</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>75,74%</t>
+          <t>75,9%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>80,15%</t>
+          <t>80,39%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1053538</t>
+          <t>1052363</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1148063</t>
+          <t>1149567</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>44,85%</t>
+          <t>44,8%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>48,88%</t>
+          <t>48,94%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2106175</t>
+          <t>2108241</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2228177</t>
+          <t>2224077</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>56,73%</t>
+          <t>56,79%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>60,02%</t>
+          <t>59,91%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>270685</t>
+          <t>267409</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>330791</t>
+          <t>328558</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>19,61%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>24,1%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1200871</t>
+          <t>1199367</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1295396</t>
+          <t>1296571</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>51,12%</t>
+          <t>51,06%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>55,15%</t>
+          <t>55,2%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1484172</t>
+          <t>1488272</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1606174</t>
+          <t>1604108</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>39,98%</t>
+          <t>40,09%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>43,27%</t>
+          <t>43,21%</t>
         </is>
       </c>
     </row>
@@ -2141,7 +2141,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si la persona entrevistada ha trabajado anteriormente en 2012</t>
+          <t>Población según si la persona entrevistada ha trabajado anteriormente en 2012 (tasa de respuesta: 99,74%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>757493</t>
+          <t>756494</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>776517</t>
+          <t>776870</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>95,8%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,38%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>553564</t>
+          <t>558442</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>628381</t>
+          <t>628704</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>46,29%</t>
+          <t>46,7%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>52,55%</t>
+          <t>52,58%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1319362</t>
+          <t>1322639</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1401304</t>
+          <t>1405917</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>66,45%</t>
+          <t>66,62%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>70,58%</t>
+          <t>70,81%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13122</t>
+          <t>12769</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>32146</t>
+          <t>33145</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>567390</t>
+          <t>567067</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>642207</t>
+          <t>637329</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>47,45%</t>
+          <t>47,42%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>53,71%</t>
+          <t>53,3%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>584106</t>
+          <t>579493</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>666048</t>
+          <t>662771</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>29,42%</t>
+          <t>29,19%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>33,55%</t>
+          <t>33,38%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>797222</t>
+          <t>794084</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>848933</t>
+          <t>847166</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>76,56%</t>
+          <t>76,26%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>81,52%</t>
+          <t>81,35%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>697045</t>
+          <t>696581</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>763057</t>
+          <t>766231</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>59,38%</t>
+          <t>59,34%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>65,01%</t>
+          <t>65,28%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1510261</t>
+          <t>1509556</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1600835</t>
+          <t>1598506</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>68,18%</t>
+          <t>68,15%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>72,27%</t>
+          <t>72,16%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>192420</t>
+          <t>194187</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>244131</t>
+          <t>247269</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>18,65%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>23,44%</t>
+          <t>23,74%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>410749</t>
+          <t>407575</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>476761</t>
+          <t>477225</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>34,99%</t>
+          <t>34,72%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>40,62%</t>
+          <t>40,66%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>614325</t>
+          <t>616654</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>704899</t>
+          <t>705604</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>27,73%</t>
+          <t>27,84%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>31,82%</t>
+          <t>31,85%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>123921</t>
+          <t>124273</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>142350</t>
+          <t>142495</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>76,54%</t>
+          <t>76,76%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>87,93%</t>
+          <t>88,01%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>143744</t>
+          <t>143152</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>172672</t>
+          <t>170935</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>64,54%</t>
+          <t>64,28%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>77,53%</t>
+          <t>76,75%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>273979</t>
+          <t>274922</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>308783</t>
+          <t>310373</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>71,23%</t>
+          <t>71,48%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>80,28%</t>
+          <t>80,7%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>19549</t>
+          <t>19404</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>37978</t>
+          <t>37626</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>23,46%</t>
+          <t>23,24%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>50043</t>
+          <t>51780</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>78971</t>
+          <t>79563</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>22,47%</t>
+          <t>23,25%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>35,46%</t>
+          <t>35,72%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>75831</t>
+          <t>74241</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>110635</t>
+          <t>109692</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>19,3%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>28,77%</t>
+          <t>28,52%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1696566</t>
+          <t>1693144</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1757434</t>
+          <t>1754838</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>85,13%</t>
+          <t>84,96%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>88,19%</t>
+          <t>88,05%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1432039</t>
+          <t>1428341</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1533744</t>
+          <t>1535939</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>55,24%</t>
+          <t>55,1%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>59,17%</t>
+          <t>59,25%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3148592</t>
+          <t>3148336</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3268832</t>
+          <t>3268113</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>68,67%</t>
+          <t>68,66%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>71,29%</t>
+          <t>71,28%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>235457</t>
+          <t>238053</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>296325</t>
+          <t>299747</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1058549</t>
+          <t>1056354</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1160254</t>
+          <t>1163952</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>40,83%</t>
+          <t>40,75%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>44,76%</t>
+          <t>44,9%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1316352</t>
+          <t>1317071</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1436592</t>
+          <t>1436848</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>28,72%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>31,33%</t>
+          <t>31,34%</t>
         </is>
       </c>
     </row>
@@ -3744,7 +3744,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si la persona entrevistada ha trabajado anteriormente en 2016</t>
+          <t>Población según si la persona entrevistada ha trabajado anteriormente en 2016 (tasa de respuesta: 99,62%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>590186</t>
+          <t>589835</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>603993</t>
+          <t>604206</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>417783</t>
+          <t>415224</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>480061</t>
+          <t>479522</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>45,62%</t>
+          <t>45,34%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>52,42%</t>
+          <t>52,36%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1008080</t>
+          <t>1008990</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1083749</t>
+          <t>1081310</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>66,02%</t>
+          <t>66,08%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>70,97%</t>
+          <t>70,81%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7236</t>
+          <t>7023</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>21043</t>
+          <t>21394</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>435701</t>
+          <t>436240</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>497979</t>
+          <t>500538</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>47,58%</t>
+          <t>47,64%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>54,38%</t>
+          <t>54,66%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>443242</t>
+          <t>445681</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>518911</t>
+          <t>518001</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>29,03%</t>
+          <t>29,19%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>33,98%</t>
+          <t>33,92%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>888774</t>
+          <t>894831</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>946822</t>
+          <t>948715</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>77,43%</t>
+          <t>77,96%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>82,49%</t>
+          <t>82,65%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>745024</t>
+          <t>742684</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>817182</t>
+          <t>814100</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>56,0%</t>
+          <t>55,83%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>61,43%</t>
+          <t>61,19%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1651907</t>
+          <t>1649428</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1744008</t>
+          <t>1748343</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>66,66%</t>
+          <t>66,56%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>70,37%</t>
+          <t>70,55%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>201047</t>
+          <t>199154</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>259095</t>
+          <t>253038</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>17,35%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>22,57%</t>
+          <t>22,04%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>513161</t>
+          <t>516243</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>585319</t>
+          <t>587659</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>38,57%</t>
+          <t>38,81%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>44,0%</t>
+          <t>44,17%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>734204</t>
+          <t>729869</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>826305</t>
+          <t>828784</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>29,63%</t>
+          <t>29,45%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>33,34%</t>
+          <t>33,44%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>135346</t>
+          <t>134668</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>159807</t>
+          <t>160252</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>70,05%</t>
+          <t>69,7%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>82,71%</t>
+          <t>82,94%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>166406</t>
+          <t>165272</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>192832</t>
+          <t>193213</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>69,14%</t>
+          <t>68,67%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>80,12%</t>
+          <t>80,28%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>310326</t>
+          <t>307321</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>346906</t>
+          <t>344917</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>71,52%</t>
+          <t>70,83%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>79,95%</t>
+          <t>79,49%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>33418</t>
+          <t>32973</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>57879</t>
+          <t>58557</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>29,95%</t>
+          <t>30,3%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>47855</t>
+          <t>47474</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>74281</t>
+          <t>75415</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>19,72%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>30,86%</t>
+          <t>31,33%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>87006</t>
+          <t>88995</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>123586</t>
+          <t>126591</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>20,51%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>28,48%</t>
+          <t>29,17%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1637145</t>
+          <t>1634218</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1700956</t>
+          <t>1698265</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>83,86%</t>
+          <t>83,71%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>87,12%</t>
+          <t>86,99%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1355411</t>
+          <t>1356171</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1456875</t>
+          <t>1458469</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>54,5%</t>
+          <t>54,53%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>58,58%</t>
+          <t>58,65%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3008919</t>
+          <t>3007334</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3134277</t>
+          <t>3137441</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>67,78%</t>
+          <t>67,75%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>70,61%</t>
+          <t>70,68%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>251367</t>
+          <t>254058</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>315178</t>
+          <t>318105</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1029917</t>
+          <t>1028323</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1131381</t>
+          <t>1130621</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>41,42%</t>
+          <t>41,35%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>45,5%</t>
+          <t>45,47%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1304838</t>
+          <t>1301674</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1430196</t>
+          <t>1431781</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>29,39%</t>
+          <t>29,32%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>32,22%</t>
+          <t>32,25%</t>
         </is>
       </c>
     </row>
@@ -5347,7 +5347,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si la persona entrevistada ha trabajado anteriormente en 2023</t>
+          <t>Población según si la persona entrevistada ha trabajado anteriormente en 2023 (tasa de respuesta: 98,94%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5542,12 +5542,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>367778</t>
+          <t>370142</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>380169</t>
+          <t>380654</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>96,68%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,43%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>342517</t>
+          <t>345642</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>384651</t>
+          <t>381726</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>51,29%</t>
+          <t>51,76%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>57,6%</t>
+          <t>57,16%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>714482</t>
+          <t>715086</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>760923</t>
+          <t>762582</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5627,12 +5627,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>68,0%</t>
+          <t>68,06%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>72,42%</t>
+          <t>72,58%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2667</t>
+          <t>2182</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15058</t>
+          <t>12694</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>283181</t>
+          <t>286106</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>325315</t>
+          <t>322190</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>42,4%</t>
+          <t>42,84%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>48,71%</t>
+          <t>48,24%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>289745</t>
+          <t>288086</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>336186</t>
+          <t>335582</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>27,58%</t>
+          <t>27,42%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>32,0%</t>
+          <t>31,94%</t>
         </is>
       </c>
     </row>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>623358</t>
+          <t>623157</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>708340</t>
+          <t>705633</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>71,36%</t>
+          <t>71,34%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>81,09%</t>
+          <t>80,78%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>760071</t>
+          <t>762988</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1028222</t>
+          <t>1028180</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>60,13%</t>
+          <t>60,36%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>81,35%</t>
+          <t>81,34%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1430168</t>
+          <t>1432008</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1680580</t>
+          <t>1689840</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>66,91%</t>
+          <t>66,99%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>78,62%</t>
+          <t>79,06%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>165150</t>
+          <t>167857</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>250132</t>
+          <t>250333</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>28,64%</t>
+          <t>28,66%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>235783</t>
+          <t>235825</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>503934</t>
+          <t>501017</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>18,66%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>39,87%</t>
+          <t>39,64%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>456915</t>
+          <t>447655</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>707327</t>
+          <t>705487</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>21,38%</t>
+          <t>20,94%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>33,09%</t>
+          <t>33,01%</t>
         </is>
       </c>
     </row>
@@ -6228,12 +6228,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>149255</t>
+          <t>148628</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>173623</t>
+          <t>173840</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>78,54%</t>
+          <t>78,21%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>91,36%</t>
+          <t>91,47%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>161315</t>
+          <t>159873</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>184737</t>
+          <t>184068</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>75,09%</t>
+          <t>74,42%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>85,99%</t>
+          <t>85,68%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>317927</t>
+          <t>318375</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>352074</t>
+          <t>353047</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>78,52%</t>
+          <t>78,63%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>86,96%</t>
+          <t>87,2%</t>
         </is>
       </c>
     </row>
@@ -6341,12 +6341,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>16421</t>
+          <t>16204</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>40789</t>
+          <t>41416</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>21,79%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>30099</t>
+          <t>30768</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>53521</t>
+          <t>54963</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>25,58%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>52806</t>
+          <t>51833</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>86953</t>
+          <t>86505</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>21,48%</t>
+          <t>21,37%</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1150964</t>
+          <t>1150941</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1247152</t>
+          <t>1247533</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>79,58%</t>
+          <t>79,57%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>86,23%</t>
+          <t>86,25%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1294834</t>
+          <t>1296440</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1615879</t>
+          <t>1613548</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>60,32%</t>
+          <t>60,39%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>75,27%</t>
+          <t>75,17%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2511014</t>
+          <t>2513104</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2773412</t>
+          <t>2779496</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>69,89%</t>
+          <t>69,94%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>77,19%</t>
+          <t>77,36%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>199218</t>
+          <t>198837</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>295406</t>
+          <t>295429</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>20,43%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>530794</t>
+          <t>533125</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>851839</t>
+          <t>850233</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>24,73%</t>
+          <t>24,83%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>39,68%</t>
+          <t>39,61%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>819630</t>
+          <t>813546</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1082028</t>
+          <t>1079938</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>22,81%</t>
+          <t>22,64%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>30,11%</t>
+          <t>30,06%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P63-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P63-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>598212</t>
+          <t>597710</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>621599</t>
+          <t>623044</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>91,82%</t>
+          <t>91,74%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,63%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>435543</t>
+          <t>436371</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>502909</t>
+          <t>505040</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>37,5%</t>
+          <t>37,57%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>43,3%</t>
+          <t>43,48%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1039430</t>
+          <t>1039421</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1122738</t>
+          <t>1121674</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>61,92%</t>
+          <t>61,87%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>29919</t>
+          <t>28474</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>53306</t>
+          <t>53808</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>658661</t>
+          <t>656530</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>726027</t>
+          <t>725199</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>56,7%</t>
+          <t>56,52%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>62,5%</t>
+          <t>62,43%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>690350</t>
+          <t>691414</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>773658</t>
+          <t>773667</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>38,08%</t>
+          <t>38,13%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>318391</t>
+          <t>318543</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>364139</t>
+          <t>364870</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>56,27%</t>
+          <t>56,3%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>64,36%</t>
+          <t>64,49%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>476117</t>
+          <t>476096</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>541473</t>
+          <t>538873</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>54,02%</t>
+          <t>53,76%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>812634</t>
+          <t>809523</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>887938</t>
+          <t>888944</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>51,82%</t>
+          <t>51,62%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>56,62%</t>
+          <t>56,69%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>201660</t>
+          <t>200929</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>247408</t>
+          <t>247256</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>35,64%</t>
+          <t>35,51%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>43,73%</t>
+          <t>43,7%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>460837</t>
+          <t>463437</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>526193</t>
+          <t>526214</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>45,98%</t>
+          <t>46,24%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>680171</t>
+          <t>679165</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>755475</t>
+          <t>758586</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>43,38%</t>
+          <t>43,31%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>48,18%</t>
+          <t>48,38%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>102126</t>
+          <t>101261</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>122997</t>
+          <t>122247</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>69,9%</t>
+          <t>69,31%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>84,19%</t>
+          <t>83,67%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>110955</t>
+          <t>110221</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>136328</t>
+          <t>135279</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>59,96%</t>
+          <t>59,56%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>73,67%</t>
+          <t>73,1%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>222265</t>
+          <t>219470</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>253720</t>
+          <t>252975</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>67,12%</t>
+          <t>66,27%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>76,62%</t>
+          <t>76,39%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>23101</t>
+          <t>23851</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>43972</t>
+          <t>44837</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>30,1%</t>
+          <t>30,69%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>48726</t>
+          <t>49775</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>74099</t>
+          <t>74833</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>26,33%</t>
+          <t>26,9%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>40,04%</t>
+          <t>40,44%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>77432</t>
+          <t>78177</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>108887</t>
+          <t>111682</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>23,38%</t>
+          <t>23,61%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>32,88%</t>
+          <t>33,73%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1034857</t>
+          <t>1037410</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1096006</t>
+          <t>1097737</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>75,9%</t>
+          <t>76,09%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>80,39%</t>
+          <t>80,51%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1052363</t>
+          <t>1049832</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1149567</t>
+          <t>1146176</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>44,8%</t>
+          <t>44,69%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>48,94%</t>
+          <t>48,8%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2108241</t>
+          <t>2105268</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2224077</t>
+          <t>2228217</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>56,79%</t>
+          <t>56,71%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>59,91%</t>
+          <t>60,02%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>267409</t>
+          <t>265678</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>328558</t>
+          <t>326005</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>19,49%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>23,91%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1199367</t>
+          <t>1202758</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1296571</t>
+          <t>1299102</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>51,06%</t>
+          <t>51,2%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>55,2%</t>
+          <t>55,31%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1488272</t>
+          <t>1484132</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1604108</t>
+          <t>1607081</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>40,09%</t>
+          <t>39,98%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>43,21%</t>
+          <t>43,29%</t>
         </is>
       </c>
     </row>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>756494</t>
+          <t>756649</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>776870</t>
+          <t>776945</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>95,82%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>558442</t>
+          <t>558566</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>628704</t>
+          <t>627809</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>46,7%</t>
+          <t>46,71%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>52,58%</t>
+          <t>52,5%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1322639</t>
+          <t>1316864</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1405917</t>
+          <t>1401295</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>66,62%</t>
+          <t>66,33%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>70,81%</t>
+          <t>70,58%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12769</t>
+          <t>12694</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>33145</t>
+          <t>32990</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>567067</t>
+          <t>567962</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>637329</t>
+          <t>637205</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>47,42%</t>
+          <t>47,5%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>53,3%</t>
+          <t>53,29%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>579493</t>
+          <t>584115</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>662771</t>
+          <t>668546</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>29,19%</t>
+          <t>29,42%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>33,38%</t>
+          <t>33,67%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>794084</t>
+          <t>798503</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>847166</t>
+          <t>850460</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>76,26%</t>
+          <t>76,68%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>81,35%</t>
+          <t>81,67%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>696581</t>
+          <t>697330</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>766231</t>
+          <t>765473</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>59,34%</t>
+          <t>59,41%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>65,28%</t>
+          <t>65,21%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1509556</t>
+          <t>1509306</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1598506</t>
+          <t>1597388</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>68,15%</t>
+          <t>68,14%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>72,16%</t>
+          <t>72,11%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>194187</t>
+          <t>190893</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>247269</t>
+          <t>242850</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>18,33%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>23,32%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>407575</t>
+          <t>408333</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>477225</t>
+          <t>476476</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>34,72%</t>
+          <t>34,79%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>40,66%</t>
+          <t>40,59%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>616654</t>
+          <t>617772</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>705604</t>
+          <t>705854</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>27,84%</t>
+          <t>27,89%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>31,85%</t>
+          <t>31,86%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>124273</t>
+          <t>124202</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>142495</t>
+          <t>142689</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>76,76%</t>
+          <t>76,72%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>88,01%</t>
+          <t>88,13%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>143152</t>
+          <t>144225</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>170935</t>
+          <t>172108</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>64,28%</t>
+          <t>64,76%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>76,75%</t>
+          <t>77,28%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>274922</t>
+          <t>274604</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>310373</t>
+          <t>308245</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>71,48%</t>
+          <t>71,4%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>80,7%</t>
+          <t>80,14%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>19404</t>
+          <t>19210</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>37626</t>
+          <t>37697</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>23,24%</t>
+          <t>23,28%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>51780</t>
+          <t>50607</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>79563</t>
+          <t>78490</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>22,72%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>35,72%</t>
+          <t>35,24%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>74241</t>
+          <t>76369</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>109692</t>
+          <t>110010</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>19,3%</t>
+          <t>19,86%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>28,52%</t>
+          <t>28,6%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1693144</t>
+          <t>1698455</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1754838</t>
+          <t>1756904</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>84,96%</t>
+          <t>85,23%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>88,05%</t>
+          <t>88,16%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1428341</t>
+          <t>1433264</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1535939</t>
+          <t>1534834</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>55,1%</t>
+          <t>55,29%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>59,25%</t>
+          <t>59,21%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3148336</t>
+          <t>3143226</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3268113</t>
+          <t>3269649</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>68,66%</t>
+          <t>68,55%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>71,28%</t>
+          <t>71,31%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>238053</t>
+          <t>235987</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>299747</t>
+          <t>294436</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1056354</t>
+          <t>1057459</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1163952</t>
+          <t>1159029</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>40,75%</t>
+          <t>40,79%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>44,9%</t>
+          <t>44,71%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1317071</t>
+          <t>1315535</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1436848</t>
+          <t>1441958</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>28,72%</t>
+          <t>28,69%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>31,34%</t>
+          <t>31,45%</t>
         </is>
       </c>
     </row>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>589835</t>
+          <t>589923</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>604206</t>
+          <t>604098</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,51%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>415224</t>
+          <t>417235</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>479522</t>
+          <t>477968</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>45,34%</t>
+          <t>45,56%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>52,36%</t>
+          <t>52,19%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1008990</t>
+          <t>1010224</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1081310</t>
+          <t>1086455</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>66,08%</t>
+          <t>66,16%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>70,81%</t>
+          <t>71,15%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7023</t>
+          <t>7131</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>21394</t>
+          <t>21306</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>436240</t>
+          <t>437794</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>500538</t>
+          <t>498527</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>47,64%</t>
+          <t>47,81%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>54,66%</t>
+          <t>54,44%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>445681</t>
+          <t>440536</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>518001</t>
+          <t>516767</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>29,19%</t>
+          <t>28,85%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>33,92%</t>
+          <t>33,84%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>894831</t>
+          <t>892452</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>948715</t>
+          <t>946762</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>77,96%</t>
+          <t>77,75%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>82,65%</t>
+          <t>82,48%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>742684</t>
+          <t>743651</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>814100</t>
+          <t>820193</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>55,83%</t>
+          <t>55,9%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>61,19%</t>
+          <t>61,65%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1649428</t>
+          <t>1651702</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1748343</t>
+          <t>1748060</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>66,56%</t>
+          <t>66,65%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>70,55%</t>
+          <t>70,54%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>199154</t>
+          <t>201107</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>253038</t>
+          <t>255417</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>22,25%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>516243</t>
+          <t>510150</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>587659</t>
+          <t>586692</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>38,81%</t>
+          <t>38,35%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>44,17%</t>
+          <t>44,1%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>729869</t>
+          <t>730152</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>828784</t>
+          <t>826510</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>29,45%</t>
+          <t>29,46%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>33,44%</t>
+          <t>33,35%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>134668</t>
+          <t>134540</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>160252</t>
+          <t>158600</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>69,7%</t>
+          <t>69,63%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>82,94%</t>
+          <t>82,08%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>165272</t>
+          <t>167111</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>193213</t>
+          <t>193105</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>68,67%</t>
+          <t>69,43%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>80,28%</t>
+          <t>80,23%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>307321</t>
+          <t>310613</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>344917</t>
+          <t>347476</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>70,83%</t>
+          <t>71,58%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>79,49%</t>
+          <t>80,08%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>32973</t>
+          <t>34625</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>58557</t>
+          <t>58685</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>17,92%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>30,3%</t>
+          <t>30,37%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>47474</t>
+          <t>47582</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>75415</t>
+          <t>73576</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>19,77%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>31,33%</t>
+          <t>30,57%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>88995</t>
+          <t>86436</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>126591</t>
+          <t>123299</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>19,92%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>29,17%</t>
+          <t>28,42%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1634218</t>
+          <t>1632634</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1698265</t>
+          <t>1697784</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>83,71%</t>
+          <t>83,63%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>86,99%</t>
+          <t>86,96%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1356171</t>
+          <t>1352094</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1458469</t>
+          <t>1456553</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>54,53%</t>
+          <t>54,37%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>58,65%</t>
+          <t>58,57%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3007334</t>
+          <t>3014839</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3137441</t>
+          <t>3138380</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>67,75%</t>
+          <t>67,92%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>70,68%</t>
+          <t>70,7%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>254058</t>
+          <t>254539</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>318105</t>
+          <t>319689</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>16,37%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1028323</t>
+          <t>1030239</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1130621</t>
+          <t>1134698</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>41,35%</t>
+          <t>41,43%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>45,47%</t>
+          <t>45,63%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1301674</t>
+          <t>1300735</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1431781</t>
+          <t>1424276</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>29,32%</t>
+          <t>29,3%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>32,25%</t>
+          <t>32,08%</t>
         </is>
       </c>
     </row>
@@ -5537,32 +5537,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>376837</t>
+          <t>408646</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>370142</t>
+          <t>401612</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>380654</t>
+          <t>412113</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,57%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,4%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5572,32 +5572,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>363391</t>
+          <t>399004</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>345642</t>
+          <t>377715</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>381726</t>
+          <t>417964</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>54,41%</t>
+          <t>54,82%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>51,76%</t>
+          <t>51,9%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>57,16%</t>
+          <t>57,43%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>740228</t>
+          <t>807650</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>715086</t>
+          <t>781274</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>762582</t>
+          <t>830314</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>70,45%</t>
+          <t>70,7%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>68,06%</t>
+          <t>68,39%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>72,58%</t>
+          <t>72,68%</t>
         </is>
       </c>
     </row>
@@ -5650,32 +5650,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5999</t>
+          <t>5949</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2182</t>
+          <t>2482</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12694</t>
+          <t>12983</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5685,32 +5685,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>304441</t>
+          <t>328801</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>286106</t>
+          <t>309841</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>322190</t>
+          <t>350090</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>45,59%</t>
+          <t>45,18%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>42,84%</t>
+          <t>42,57%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>48,24%</t>
+          <t>48,1%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>310440</t>
+          <t>334750</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>288086</t>
+          <t>312086</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>335582</t>
+          <t>361126</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>29,55%</t>
+          <t>29,3%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>27,42%</t>
+          <t>27,32%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>31,94%</t>
+          <t>31,61%</t>
         </is>
       </c>
     </row>
@@ -5763,17 +5763,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>382836</t>
+          <t>414595</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>382836</t>
+          <t>414595</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>382836</t>
+          <t>414595</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5798,17 +5798,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>667832</t>
+          <t>727805</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>667832</t>
+          <t>727805</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>667832</t>
+          <t>727805</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1050668</t>
+          <t>1142400</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1050668</t>
+          <t>1142400</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1050668</t>
+          <t>1142400</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5880,32 +5880,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>666534</t>
+          <t>723254</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>623157</t>
+          <t>682181</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>705633</t>
+          <t>756107</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>76,31%</t>
+          <t>78,33%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>71,34%</t>
+          <t>73,88%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>80,78%</t>
+          <t>81,89%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5915,32 +5915,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>852249</t>
+          <t>727351</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>762988</t>
+          <t>696087</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1028180</t>
+          <t>760666</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>67,42%</t>
+          <t>60,92%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>60,36%</t>
+          <t>58,3%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>81,34%</t>
+          <t>63,71%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>1518783</t>
+          <t>1450606</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1432008</t>
+          <t>1396168</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1689840</t>
+          <t>1496604</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>71,05%</t>
+          <t>68,51%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>66,99%</t>
+          <t>65,94%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>79,06%</t>
+          <t>70,69%</t>
         </is>
       </c>
     </row>
@@ -5993,32 +5993,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>206956</t>
+          <t>200121</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>167857</t>
+          <t>167268</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>250333</t>
+          <t>241194</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>21,67%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>19,22%</t>
+          <t>18,11%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>28,66%</t>
+          <t>26,12%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6028,32 +6028,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>411756</t>
+          <t>466540</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>235825</t>
+          <t>433225</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>501017</t>
+          <t>497804</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>32,58%</t>
+          <t>39,08%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>18,66%</t>
+          <t>36,29%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>39,64%</t>
+          <t>41,7%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>618712</t>
+          <t>666661</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>447655</t>
+          <t>620663</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>705487</t>
+          <t>721099</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>28,95%</t>
+          <t>31,49%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>29,31%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>33,01%</t>
+          <t>34,06%</t>
         </is>
       </c>
     </row>
@@ -6106,17 +6106,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>873490</t>
+          <t>923375</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>873490</t>
+          <t>923375</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>873490</t>
+          <t>923375</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6141,17 +6141,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1264005</t>
+          <t>1193891</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1264005</t>
+          <t>1193891</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1264005</t>
+          <t>1193891</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2137495</t>
+          <t>2117267</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2137495</t>
+          <t>2117267</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2137495</t>
+          <t>2117267</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6223,32 +6223,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>162491</t>
+          <t>183281</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>148628</t>
+          <t>167839</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>173840</t>
+          <t>195122</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>85,5%</t>
+          <t>85,47%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>78,21%</t>
+          <t>78,27%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>91,47%</t>
+          <t>90,99%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6258,32 +6258,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>173483</t>
+          <t>198744</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>159873</t>
+          <t>185179</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>184068</t>
+          <t>210378</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>80,75%</t>
+          <t>80,8%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>74,42%</t>
+          <t>75,29%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>85,68%</t>
+          <t>85,53%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,17 +6293,17 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>335974</t>
+          <t>382026</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>318375</t>
+          <t>362408</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>353047</t>
+          <t>400458</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>78,63%</t>
+          <t>78,71%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>87,2%</t>
+          <t>86,98%</t>
         </is>
       </c>
     </row>
@@ -6336,32 +6336,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>27553</t>
+          <t>31158</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>16204</t>
+          <t>19317</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>41416</t>
+          <t>46600</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>21,73%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6371,32 +6371,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>41353</t>
+          <t>47226</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>30768</t>
+          <t>35592</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>54963</t>
+          <t>60791</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>19,2%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>25,58%</t>
+          <t>24,71%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6406,17 +6406,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>68906</t>
+          <t>78383</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>51833</t>
+          <t>59951</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>86505</t>
+          <t>98001</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>21,37%</t>
+          <t>21,29%</t>
         </is>
       </c>
     </row>
@@ -6449,17 +6449,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>190044</t>
+          <t>214439</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>190044</t>
+          <t>214439</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>190044</t>
+          <t>214439</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6484,17 +6484,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>214836</t>
+          <t>245970</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>214836</t>
+          <t>245970</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>214836</t>
+          <t>245970</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>404880</t>
+          <t>460409</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>404880</t>
+          <t>460409</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>404880</t>
+          <t>460409</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6566,32 +6566,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1205863</t>
+          <t>1315181</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1150941</t>
+          <t>1272481</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1247533</t>
+          <t>1354170</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>83,37%</t>
+          <t>84,72%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>79,57%</t>
+          <t>81,97%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>86,25%</t>
+          <t>87,23%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6601,32 +6601,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1389124</t>
+          <t>1325100</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1296440</t>
+          <t>1283078</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1613548</t>
+          <t>1368642</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>64,71%</t>
+          <t>61,13%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>60,39%</t>
+          <t>59,19%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>75,17%</t>
+          <t>63,14%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>2594985</t>
+          <t>2640282</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2513104</t>
+          <t>2574083</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2779496</t>
+          <t>2693105</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>72,22%</t>
+          <t>70,97%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>69,94%</t>
+          <t>69,19%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>77,36%</t>
+          <t>72,39%</t>
         </is>
       </c>
     </row>
@@ -6679,32 +6679,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>198837</t>
+          <t>198239</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>295429</t>
+          <t>279928</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>15,28%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6714,32 +6714,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>757549</t>
+          <t>842567</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>533125</t>
+          <t>799025</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>850233</t>
+          <t>884589</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>35,29%</t>
+          <t>38,87%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>24,83%</t>
+          <t>36,86%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>39,61%</t>
+          <t>40,81%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>998057</t>
+          <t>1079794</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>813546</t>
+          <t>1026971</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1079938</t>
+          <t>1145993</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>27,78%</t>
+          <t>29,03%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>22,64%</t>
+          <t>27,61%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>30,06%</t>
+          <t>30,81%</t>
         </is>
       </c>
     </row>
@@ -6792,17 +6792,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1446370</t>
+          <t>1552409</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1446370</t>
+          <t>1552409</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1446370</t>
+          <t>1552409</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6827,17 +6827,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2146673</t>
+          <t>2167667</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2146673</t>
+          <t>2167667</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2146673</t>
+          <t>2167667</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>3593042</t>
+          <t>3720076</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>3593042</t>
+          <t>3720076</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>3593042</t>
+          <t>3720076</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
